--- a/VerveStacks_FRA_grids_kan25/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_FRA_grids_kan25/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_kan25\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{32B3E9FF-8AD9-444B-A942-6E9AFC11C831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{523E7163-D38D-4C70-8E1E-C96ACB438376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3573,7 +3573,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D35391C2-B36D-48EF-8CEB-1C88D30198C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18D0248F-EF80-4D2E-9468-9D9489EB2E78}">
   <dimension ref="B2:AG601"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -13804,7 +13804,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2FE3BCB-6709-4E32-BD9D-A11CAAE97889}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8DE66D-DD91-438E-89D3-6723E4A0E7C0}">
   <dimension ref="B9:L64"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -28595,7 +28595,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F24FDC3-A22A-4F4E-AF90-1ECF927FC958}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD545449-9FD3-472F-8D67-0BFECFD0263C}">
   <dimension ref="A1:I79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_FRA_grids_kan25/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_FRA_grids_kan25/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_kan25\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A23C876B-2A0D-4049-A16C-2C4C56C01558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7D202BB-0ABB-4B05-AB65-18DBB8DA85A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3417,7 +3417,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF327E26-B283-46EE-8D79-B37A282DBD0A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF5AF743-2E1F-4810-B0AD-C0F870992B17}">
   <dimension ref="B2:AG549"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12920,7 +12920,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89046210-5D10-4D4D-9FDC-0560079E4DCB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{762BFE26-5F26-43D4-97CC-69FE857AEA37}">
   <dimension ref="B9:L64"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27711,7 +27711,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6075DCE-9B7B-43B7-8AC4-D8B2ECAE1B09}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD3BCC56-A048-4114-985C-A74A9E153CCE}">
   <dimension ref="A1:I79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
